--- a/artfynd/A 25183-2022 artfynd.xlsx
+++ b/artfynd/A 25183-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121095491</v>
       </c>
       <c r="B2" t="n">
-        <v>88458</v>
+        <v>88464</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121095490</v>
       </c>
       <c r="B3" t="n">
-        <v>88648</v>
+        <v>88654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 25183-2022 artfynd.xlsx
+++ b/artfynd/A 25183-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121095491</v>
+        <v>121095490</v>
       </c>
       <c r="B2" t="n">
-        <v>88464</v>
+        <v>88654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,23 +691,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4374</v>
+        <v>4392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Wünsche</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121095490</v>
+        <v>121095491</v>
       </c>
       <c r="B3" t="n">
-        <v>88654</v>
+        <v>88464</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,19 +802,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4392</v>
+        <v>4374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Gul vaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>

--- a/artfynd/A 25183-2022 artfynd.xlsx
+++ b/artfynd/A 25183-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121095490</v>
+        <v>121095491</v>
       </c>
       <c r="B2" t="n">
-        <v>88654</v>
+        <v>88471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,19 +691,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4392</v>
+        <v>4374</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Gul vaxskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121095491</v>
+        <v>121095490</v>
       </c>
       <c r="B3" t="n">
-        <v>88464</v>
+        <v>88661</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,23 +806,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4374</v>
+        <v>4392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Wünsche</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>

--- a/artfynd/A 25183-2022 artfynd.xlsx
+++ b/artfynd/A 25183-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121095491</v>
       </c>
       <c r="B2" t="n">
-        <v>88471</v>
+        <v>88474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121095490</v>
       </c>
       <c r="B3" t="n">
-        <v>88661</v>
+        <v>88664</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 25183-2022 artfynd.xlsx
+++ b/artfynd/A 25183-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121095491</v>
+        <v>16559111</v>
       </c>
       <c r="B2" t="n">
-        <v>88474</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4374</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horn Lillstugan 1, Srm</t>
+          <t>Horn-Lillstugan, 275 m OSO om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624133</v>
+        <v>624247</v>
       </c>
       <c r="R2" t="n">
-        <v>6511826</v>
+        <v>6511640</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,31 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gräs-örtrik tallskog, betad</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121095490</v>
+        <v>121095491</v>
       </c>
       <c r="B3" t="n">
-        <v>88664</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,19 +788,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4392</v>
+        <v>4374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -899,6 +885,520 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16559010</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89085</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Toppvaxing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Horn-Lillstugan, 200 m OSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>624171</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6511662</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121095490</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89029</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Horn Lillstugan 1, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>624133</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6511826</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16559004</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Horn-Lillstugan, 200 m OSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>624171</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6511662</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16559168</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Horn-Lillstugan, 325 m OSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>624286</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6511621</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>gräsrik tallskog med ängsgläntor</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16558746</v>
+      </c>
+      <c r="B8" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Horn, Lillstugan - 180 m O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>624154</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6511741</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-09-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>örtrik torräng</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25183-2022 artfynd.xlsx
+++ b/artfynd/A 25183-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16559111</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095491</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16559010</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095490</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16559004</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16559168</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,8 +1433,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16558746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>